--- a/excel-files/NAVOTAS/WAWA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/WAWA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{100BE943-9126-4F1B-AA29-5AF47CA994F9}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{780AECDB-2170-45B4-AE2F-AF0B2E2F0DDE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -3703,17 +3703,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1">
+        <v>60</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3806,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3876,7 +3884,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3896,7 +3904,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>61</v>
@@ -3908,7 +3916,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3936,7 +3944,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3964,7 +3972,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3982,17 +3990,25 @@
       <c r="B25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="C25" s="1">
+        <v>61</v>
+      </c>
+      <c r="D25" s="1">
+        <v>97</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1">
@@ -4000,19 +4016,27 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>61</v>
+      </c>
+      <c r="D26" s="1">
+        <v>97</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1">
@@ -4032,7 +4056,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
@@ -4070,17 +4094,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>61</v>
+      </c>
+      <c r="D29" s="1">
+        <v>97</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4098,19 +4130,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>69</v>
+      </c>
+      <c r="D31" s="1">
+        <v>86</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4118,7 +4158,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4190,7 +4230,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4206,19 +4246,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>69</v>
+      </c>
+      <c r="D36" s="1">
+        <v>86</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4228,17 +4276,25 @@
       <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="1">
+        <v>69</v>
+      </c>
+      <c r="D37" s="1">
+        <v>86</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4248,17 +4304,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>69</v>
+      </c>
+      <c r="D38" s="1">
+        <v>86</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4296,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4316,7 +4380,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4396,7 +4460,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4486,7 +4550,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4506,7 +4570,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4586,7 +4650,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4676,7 +4740,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4696,7 +4760,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4776,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4866,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4886,7 +4950,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4966,7 +5030,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5056,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5076,7 +5140,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5156,7 +5220,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5408,10 +5472,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E2:E6 E31:E39 E14:E19 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5424,7 +5488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5999,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6068,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6600,7 +6664,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>48</v>
@@ -6683,7 +6747,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -7064,7 +7128,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>59</v>
@@ -7295,7 +7359,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>59</v>
@@ -7372,7 +7436,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>59</v>
@@ -7532,7 +7596,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7601,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7877,7 +7941,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8167,7 +8231,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>69</v>
@@ -8244,7 +8308,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>69</v>
@@ -8552,7 +8616,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8858,7 +8922,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8927,7 +8991,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9203,7 +9267,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9493,7 +9557,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9562,7 +9626,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9838,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10128,7 +10192,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10197,7 +10261,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10473,7 +10537,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10763,7 +10827,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10832,7 +10896,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11108,7 +11172,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11398,7 +11462,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11467,7 +11531,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11743,7 +11807,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13578,186 +13642,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13777,8 +13661,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 F14:F21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 L14:L21 F33:F41 F23:F31 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 X112:X127 F103:F110 R103:R110 L103:L110 X103:X110 F43:F51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14:G21 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 M14:M110 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13796,7 +13680,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14011,7 +13895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14080,7 +13964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14149,7 +14033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14218,7 +14102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14287,12 +14171,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14356,12 +14240,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14425,7 +14309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14495,7 +14379,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14564,7 +14448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14633,7 +14517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14702,7 +14586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14771,7 +14655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14840,12 +14724,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14909,12 +14793,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -14978,7 +14862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15048,7 +14932,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15117,7 +15001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15186,7 +15070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15255,12 +15139,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15324,7 +15208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15393,7 +15277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15462,12 +15346,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15531,12 +15415,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15600,7 +15484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15670,12 +15554,12 @@
       </c>
     </row>
     <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15739,12 +15623,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15808,7 +15692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15877,7 +15761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15946,7 +15830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16015,12 +15899,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16084,7 +15968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16153,7 +16037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16222,7 +16106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16291,7 +16175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16360,7 +16244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16430,12 +16314,12 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16499,12 +16383,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16568,7 +16452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16637,7 +16521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16706,7 +16590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16775,12 +16659,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -16844,7 +16728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16913,7 +16797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16982,7 +16866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17051,7 +16935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17120,7 +17004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17190,12 +17074,12 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -17259,12 +17143,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -17328,7 +17212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17397,7 +17281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17466,7 +17350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17535,12 +17419,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -17604,7 +17488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17673,7 +17557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17742,7 +17626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17811,7 +17695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17880,7 +17764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17950,12 +17834,12 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18019,12 +17903,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18088,7 +17972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18157,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18226,7 +18110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18295,12 +18179,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18364,7 +18248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18433,7 +18317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18502,7 +18386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18571,7 +18455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18640,7 +18524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18710,12 +18594,12 @@
       </c>
     </row>
     <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18779,12 +18663,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -18848,7 +18732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18917,7 +18801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18986,7 +18870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19055,12 +18939,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19124,7 +19008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19193,7 +19077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19262,7 +19146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19331,7 +19215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19400,7 +19284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19470,12 +19354,12 @@
       </c>
     </row>
     <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19539,12 +19423,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19608,7 +19492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19677,7 +19561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19746,7 +19630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19815,12 +19699,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -19884,7 +19768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19953,7 +19837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20022,7 +19906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20091,7 +19975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20160,7 +20044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20230,12 +20114,12 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20299,12 +20183,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20368,7 +20252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20437,7 +20321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20506,7 +20390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20575,12 +20459,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -20644,7 +20528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20713,7 +20597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20782,7 +20666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20851,7 +20735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20920,7 +20804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20990,7 +20874,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>25</v>
       </c>
@@ -21059,7 +20943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>25</v>
       </c>
@@ -21128,7 +21012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>25</v>
       </c>
@@ -21197,7 +21081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>25</v>
       </c>
@@ -21266,7 +21150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>25</v>
       </c>
@@ -21335,7 +21219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>25</v>
       </c>
@@ -21404,7 +21288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>25</v>
       </c>
@@ -21473,7 +21357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>25</v>
       </c>
@@ -22053,186 +21937,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22250,8 +21954,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
